--- a/astro-site/public/dl/kit-tareas-hotel/01-fb-buffet-desayuno.xlsx
+++ b/astro-site/public/dl/kit-tareas-hotel/01-fb-buffet-desayuno.xlsx
@@ -1,17 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Apertura Desayuno" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Cierre Desayuno" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Apertura Desayuno" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cierre Desayuno" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Apertura Desayuno'!$5:$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Cierre Desayuno'!$5:$5</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -19,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -80,6 +83,11 @@
       <name val="Calibri"/>
       <color rgb="00999999"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="8">
@@ -150,54 +158,65 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="19">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="2" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="5" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="6" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="7" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C8E6C9"/>
+          <bgColor rgb="00C8E6C9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -557,15 +576,16 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B12"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="3"/>
-    <col customWidth="1" max="2" min="2" width="80"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -573,6 +593,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -601,9 +622,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="B8" t="inlineStr"/>
-    </row>
+    <row r="8"/>
     <row r="9">
       <c r="B9" s="2" t="inlineStr">
         <is>
@@ -632,8 +651,25 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
+    <row r="14">
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-hotel · info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -642,18 +678,18 @@
   <sheetPr>
     <tabColor rgb="00E8F5E9"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -670,6 +706,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -923,6 +960,7 @@
       <c r="F16" s="11" t="n"/>
       <c r="G16" s="13" t="n"/>
     </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
@@ -1195,6 +1233,7 @@
       <c r="F31" s="11" t="n"/>
       <c r="G31" s="13" t="n"/>
     </row>
+    <row r="32"/>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
@@ -1372,6 +1411,7 @@
       <c r="F41" s="11" t="n"/>
       <c r="G41" s="13" t="n"/>
     </row>
+    <row r="42"/>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
@@ -1548,6 +1588,26 @@
       <c r="E51" s="12" t="n"/>
       <c r="F51" s="11" t="n"/>
       <c r="G51" s="13" t="n"/>
+    </row>
+    <row r="52">
+      <c r="B52" s="18" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="C52">
+        <f>COUNTIF(E6:E51,"✓")</f>
+        <v>3.0</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E52">
+        <f>COUNTIF(B6:B51,"?*")</f>
+        <v>40.0</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="17" t="inlineStr">
@@ -1574,12 +1634,26 @@
     <mergeCell ref="A43:G43"/>
     <mergeCell ref="A54:G54"/>
   </mergeCells>
+  <conditionalFormatting sqref="A6:G51">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$E6="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="E6 E7 E8 E9 E10 E11 E12 E13 E14 E15 E16 E20 E21 E22 E23 E24 E25 E26 E27 E28 E29 E30 E31 E35 E36 E37 E38 E39 E40 E41 E45 E46 E47 E48 E49 E50 E51" type="list">
+    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E12 E13 E14 E15 E16 E20 E21 E22 E23 E24 E25 E26 E27 E28 E29 E30 E31 E35 E36 E37 E38 E39 E40 E41 E45 E46 E47 E48 E49 E50 E51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
       <formula1>"✓,✗,—"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1588,18 +1662,18 @@
   <sheetPr>
     <tabColor rgb="00E8F5E9"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1616,6 +1690,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -1774,6 +1849,7 @@
       <c r="F11" s="11" t="n"/>
       <c r="G11" s="13" t="n"/>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
@@ -1932,6 +2008,7 @@
       <c r="F20" s="11" t="n"/>
       <c r="G20" s="13" t="n"/>
     </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
@@ -2089,6 +2166,26 @@
       <c r="E29" s="12" t="n"/>
       <c r="F29" s="11" t="n"/>
       <c r="G29" s="13" t="n"/>
+    </row>
+    <row r="30">
+      <c r="B30" s="18" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="C30">
+        <f>COUNTIF(E6:E29,"✓")</f>
+        <v>2.0</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E30">
+        <f>COUNTIF(B6:B29,"?*")</f>
+        <v>20.0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="17" t="inlineStr">
@@ -2114,11 +2211,25 @@
     <mergeCell ref="A13:G13"/>
     <mergeCell ref="A22:G22"/>
   </mergeCells>
+  <conditionalFormatting sqref="A6:G29">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$E6="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="E6 E7 E8 E9 E10 E11 E15 E16 E17 E18 E19 E20 E24 E25 E26 E27 E28 E29" type="list">
+    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E15 E16 E17 E18 E19 E20 E24 E25 E26 E27 E28 E29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
       <formula1>"✓,✗,—"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/astro-site/public/dl/kit-tareas-hotel/01-fb-buffet-desayuno.xlsx
+++ b/astro-site/public/dl/kit-tareas-hotel/01-fb-buffet-desayuno.xlsx
@@ -90,7 +90,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -133,8 +133,13 @@
         <bgColor rgb="00EFEBE9"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F5E9"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -156,11 +161,55 @@
         <color rgb="00E0E0E0"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E0E0E0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E0E0E0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E0E0E0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E0E0E0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -202,6 +251,17 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -578,7 +638,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -653,9 +713,45 @@
     </row>
     <row r="13"/>
     <row r="14">
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-hotel · info@aichef.pro</t>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Seguridad alimentaria y arranque:</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>▸ La primera sección de «Apertura Desayuno» es de higiene personal y de arranque seguro: cámaras primero (¿han aguantado la noche?), campana después, comprobación del gas y sólo entonces hornos, planchas y baño maría.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>▸ El salmón marinado o ahumado en frío y cualquier pescado que se sirva crudo necesitan congelación previa: ≥ 24 h a −20 °C o 15 h a −35 °C. Pide el certificado al proveedor y anota el lote.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>▸ Al pie de «Cierre Desayuno» tienes una tabla editable de vida útil en congelación por familia: ajústala a tu producto y a tu proveedor. Está fuera del contador porque es una referencia, no una tarea.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
+    <row r="19">
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Diseñado por John Guerrero — chef y consultor gastronómico desde 2010, en cocina desde los 17 años · johnguerrero.es</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Versión 2.0 · agosto 2026 · aichef.pro/kit-tareas-hotel · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -680,7 +776,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G54"/>
+  <dimension ref="A1:G65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -710,7 +806,7 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Cocina — Preparación (05:30-06:30)</t>
+          <t>Higiene personal y arranque seguro de la cocina</t>
         </is>
       </c>
     </row>
@@ -757,7 +853,7 @@
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>Encender hornos, planchas, baño maría y equipamiento</t>
+          <t>Uniforme y calzado de trabajo limpios, delantal cambiado y pelo recogido (gorro o redecilla)</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
@@ -776,7 +872,7 @@
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>Preparar huevos revueltos, tortilla, huevos fritos a la plancha</t>
+          <t>Sin anillos, reloj ni pulseras; uñas cortas, limpias y sin esmalte</t>
         </is>
       </c>
       <c r="C7" s="10" t="inlineStr">
@@ -795,7 +891,7 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>Preparar bacon, salchichas, tomate grillado, champiñones</t>
+          <t>Heridas y cortes cubiertos con apósito impermeable de color visible y guante encima</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
@@ -814,7 +910,7 @@
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>Montar bandeja de embutidos: jamón york, pavo, chorizo, salchichón</t>
+          <t>Lavado de manos al entrar y en cada cambio de tarea: jabón, agua caliente y papel de un solo uso</t>
         </is>
       </c>
       <c r="C9" s="10" t="inlineStr">
@@ -833,7 +929,7 @@
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>Preparar selección de quesos: manchego, brie, gouda, fresco</t>
+          <t>Declarar síntomas digestivos o respiratorios: quien los tenga no manipula alimentos</t>
         </is>
       </c>
       <c r="C10" s="10" t="inlineStr">
@@ -852,7 +948,7 @@
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>Cortar fruta fresca de temporada: melón, sandía, piña, kiwi, fresas</t>
+          <t>Comprobar que las cámaras y neveras de la cocina de desayunos han funcionado toda la noche y registrar la temperatura (refrigeración 0-4 °C / congelación ≤ −18 °C) — anota la lectura: ____ °C. Si hay desviación, no saques el género hasta valorarlo</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr">
@@ -871,7 +967,7 @@
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>Preparar yogures, granola, frutos secos y miel</t>
+          <t>Encender la campana extractora y ventilar la cocina ANTES de encender nada más</t>
         </is>
       </c>
       <c r="C12" s="10" t="inlineStr">
@@ -890,7 +986,7 @@
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>Preparar bollería: croissants, magdalenas, pain au chocolat</t>
+          <t>Si la cocina tiene gas: abrir la llave general y comprobar que NO huele a gas; si huele, no enciendas nada, ventila y avisa a mantenimiento</t>
         </is>
       </c>
       <c r="C13" s="10" t="inlineStr">
@@ -904,50 +1000,56 @@
       <c r="G13" s="13" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="B14" s="9" t="inlineStr">
-        <is>
-          <t>Preparar panes: barra, integral, centeno, tostadas, molde</t>
-        </is>
-      </c>
-      <c r="C14" s="10" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D14" s="11" t="n"/>
-      <c r="E14" s="12" t="n"/>
-      <c r="F14" s="11" t="n"/>
-      <c r="G14" s="13" t="n"/>
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Cocina — Preparación (05:30-06:30)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="B15" s="9" t="inlineStr">
-        <is>
-          <t>Preparar zumos naturales: naranja, pomelo, multifrutas</t>
-        </is>
-      </c>
-      <c r="C15" s="10" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D15" s="11" t="n"/>
-      <c r="E15" s="12" t="n"/>
-      <c r="F15" s="11" t="n"/>
-      <c r="G15" s="13" t="n"/>
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>Zona</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>Responsable</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>Hora</t>
+        </is>
+      </c>
+      <c r="G15" s="7" t="inlineStr">
+        <is>
+          <t>Notas</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>Verificar temperaturas de producto caliente (&gt;65°C) y frío (&lt;5°C)</t>
+          <t>Encender hornos, planchas, baño maría y equipamiento sólo después de la campana y del control del gas</t>
         </is>
       </c>
       <c r="C16" s="10" t="inlineStr">
@@ -960,63 +1062,75 @@
       <c r="F16" s="11" t="n"/>
       <c r="G16" s="13" t="n"/>
     </row>
-    <row r="17"/>
+    <row r="17">
+      <c r="A17" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>Preparar huevos revueltos, tortilla, huevos fritos a la plancha</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D17" s="11" t="n"/>
+      <c r="E17" s="12" t="n"/>
+      <c r="F17" s="11" t="n"/>
+      <c r="G17" s="13" t="n"/>
+    </row>
     <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>Sala — Montaje del buffet (06:00-06:45)</t>
-        </is>
-      </c>
+      <c r="A18" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>Preparar bacon, salchichas, tomate grillado, champiñones</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D18" s="11" t="n"/>
+      <c r="E18" s="12" t="n"/>
+      <c r="F18" s="11" t="n"/>
+      <c r="G18" s="13" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C19" s="7" t="inlineStr">
-        <is>
-          <t>Zona</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>Responsable</t>
-        </is>
-      </c>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F19" s="7" t="inlineStr">
-        <is>
-          <t>Hora</t>
-        </is>
-      </c>
-      <c r="G19" s="7" t="inlineStr">
-        <is>
-          <t>Notas</t>
-        </is>
-      </c>
+      <c r="A19" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>Montar bandeja de embutidos: jamón york, pavo, chorizo, salchichón</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D19" s="11" t="n"/>
+      <c r="E19" s="12" t="n"/>
+      <c r="F19" s="11" t="n"/>
+      <c r="G19" s="13" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>Verificar limpieza de mesas, buffet y suelos de sala</t>
-        </is>
-      </c>
-      <c r="C20" s="14" t="inlineStr">
-        <is>
-          <t>Sala</t>
+          <t>Preparar selección de quesos: manchego, brie, gouda, fresco</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>Cocina</t>
         </is>
       </c>
       <c r="D20" s="11" t="n"/>
@@ -1026,16 +1140,16 @@
     </row>
     <row r="21">
       <c r="A21" s="8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>Montar estación caliente: chafing dishes, fuentes, cucharas de servicio</t>
+          <t>Cortar fruta fresca de temporada: melón, sandía, piña, kiwi, fresas</t>
         </is>
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>Buffet</t>
+          <t>Cocina</t>
         </is>
       </c>
       <c r="D21" s="11" t="n"/>
@@ -1045,16 +1159,16 @@
     </row>
     <row r="22">
       <c r="A22" s="8" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>Montar estación fría: embutidos, quesos, salmón, ensaladas</t>
+          <t>Preparar yogures, granola, frutos secos y miel</t>
         </is>
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>Buffet</t>
+          <t>Cocina</t>
         </is>
       </c>
       <c r="D22" s="11" t="n"/>
@@ -1064,16 +1178,16 @@
     </row>
     <row r="23">
       <c r="A23" s="8" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>Montar estación de fruta y yogures con hielo decorativo</t>
+          <t>Preparar bollería: croissants, magdalenas, pain au chocolat</t>
         </is>
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>Buffet</t>
+          <t>Cocina</t>
         </is>
       </c>
       <c r="D23" s="11" t="n"/>
@@ -1083,16 +1197,16 @@
     </row>
     <row r="24">
       <c r="A24" s="8" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>Montar estación de bollería y panes con tostadora</t>
+          <t>Preparar panes: barra, integral, centeno, tostadas, molde</t>
         </is>
       </c>
       <c r="C24" s="10" t="inlineStr">
         <is>
-          <t>Buffet</t>
+          <t>Cocina</t>
         </is>
       </c>
       <c r="D24" s="11" t="n"/>
@@ -1102,16 +1216,16 @@
     </row>
     <row r="25">
       <c r="A25" s="8" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>Montar estación de cereales, leche, muesli y toppings</t>
+          <t>Preparar zumos naturales: naranja, pomelo, multifrutas</t>
         </is>
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t>Buffet</t>
+          <t>Cocina</t>
         </is>
       </c>
       <c r="D25" s="11" t="n"/>
@@ -1121,16 +1235,16 @@
     </row>
     <row r="26">
       <c r="A26" s="8" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>Verificar estación de bebidas: café, té, leche, zumos, agua</t>
+          <t>Verificar temperaturas de producto caliente (&gt;65 °C) y frío (&lt;5 °C)</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t>Buffet</t>
+          <t>Cocina</t>
         </is>
       </c>
       <c r="D26" s="11" t="n"/>
@@ -1138,75 +1252,63 @@
       <c r="F26" s="11" t="n"/>
       <c r="G26" s="13" t="n"/>
     </row>
-    <row r="27">
-      <c r="A27" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="B27" s="9" t="inlineStr">
-        <is>
-          <t>Colocar señalización con nombre de cada plato y alérgenos</t>
-        </is>
-      </c>
-      <c r="C27" s="10" t="inlineStr">
-        <is>
-          <t>Buffet</t>
-        </is>
-      </c>
-      <c r="D27" s="11" t="n"/>
-      <c r="E27" s="12" t="n"/>
-      <c r="F27" s="11" t="n"/>
-      <c r="G27" s="13" t="n"/>
-    </row>
+    <row r="27"/>
     <row r="28">
-      <c r="A28" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="B28" s="9" t="inlineStr">
-        <is>
-          <t>Verificar mise en place de mesas: manteles, servilletas, cubiertos</t>
-        </is>
-      </c>
-      <c r="C28" s="14" t="inlineStr">
-        <is>
-          <t>Sala</t>
-        </is>
-      </c>
-      <c r="D28" s="11" t="n"/>
-      <c r="E28" s="12" t="n"/>
-      <c r="F28" s="11" t="n"/>
-      <c r="G28" s="13" t="n"/>
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Sala — Montaje del buffet (06:00-06:45)</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="B29" s="9" t="inlineStr">
-        <is>
-          <t>Colocar mermeladas, mantequilla, miel en cada mesa</t>
-        </is>
-      </c>
-      <c r="C29" s="14" t="inlineStr">
-        <is>
-          <t>Sala</t>
-        </is>
-      </c>
-      <c r="D29" s="11" t="n"/>
-      <c r="E29" s="12" t="n"/>
-      <c r="F29" s="11" t="n"/>
-      <c r="G29" s="13" t="n"/>
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>Zona</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>Responsable</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>Hora</t>
+        </is>
+      </c>
+      <c r="G29" s="7" t="inlineStr">
+        <is>
+          <t>Notas</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="8" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>Verificar temperatura de sala (20-22°C)</t>
-        </is>
-      </c>
-      <c r="C30" s="15" t="inlineStr">
-        <is>
-          <t>Admin</t>
+          <t>Verificar limpieza de mesas, buffet y suelos de sala</t>
+        </is>
+      </c>
+      <c r="C30" s="14" t="inlineStr">
+        <is>
+          <t>Sala</t>
         </is>
       </c>
       <c r="D30" s="11" t="n"/>
@@ -1216,16 +1318,16 @@
     </row>
     <row r="31">
       <c r="A31" s="8" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>Abrir buffet a la hora exacta según estándar del hotel</t>
-        </is>
-      </c>
-      <c r="C31" s="15" t="inlineStr">
-        <is>
-          <t>Admin</t>
+          <t>Montar estación caliente: chafing dishes, fuentes, cucharas de servicio</t>
+        </is>
+      </c>
+      <c r="C31" s="10" t="inlineStr">
+        <is>
+          <t>Buffet</t>
         </is>
       </c>
       <c r="D31" s="11" t="n"/>
@@ -1233,58 +1335,70 @@
       <c r="F31" s="11" t="n"/>
       <c r="G31" s="13" t="n"/>
     </row>
-    <row r="32"/>
+    <row r="32">
+      <c r="A32" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>Montar estación fría: embutidos, quesos, salmón, ensaladas</t>
+        </is>
+      </c>
+      <c r="C32" s="10" t="inlineStr">
+        <is>
+          <t>Buffet</t>
+        </is>
+      </c>
+      <c r="D32" s="11" t="n"/>
+      <c r="E32" s="12" t="n"/>
+      <c r="F32" s="11" t="n"/>
+      <c r="G32" s="13" t="n"/>
+    </row>
     <row r="33">
-      <c r="A33" s="6" t="inlineStr">
-        <is>
-          <t>Durante el servicio de desayuno</t>
-        </is>
-      </c>
+      <c r="A33" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>Salmón marinado o ahumado en frío y cualquier pescado que se sirva crudo — prevención de ANISAKIS: usar sólo producto con congelación previa acreditada (≥ 24 h a −20 °C, o 15 h a −35 °C); si lo marinas en casa, congélalo tú antes y anota el lote</t>
+        </is>
+      </c>
+      <c r="C33" s="10" t="inlineStr">
+        <is>
+          <t>Buffet</t>
+        </is>
+      </c>
+      <c r="D33" s="11" t="n"/>
+      <c r="E33" s="12" t="n"/>
+      <c r="F33" s="11" t="n"/>
+      <c r="G33" s="13" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="7" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B34" s="7" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C34" s="7" t="inlineStr">
-        <is>
-          <t>Zona</t>
-        </is>
-      </c>
-      <c r="D34" s="7" t="inlineStr">
-        <is>
-          <t>Responsable</t>
-        </is>
-      </c>
-      <c r="E34" s="7" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F34" s="7" t="inlineStr">
-        <is>
-          <t>Hora</t>
-        </is>
-      </c>
-      <c r="G34" s="7" t="inlineStr">
-        <is>
-          <t>Notas</t>
-        </is>
-      </c>
+      <c r="A34" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>Montar estación de fruta y yogures con hielo decorativo</t>
+        </is>
+      </c>
+      <c r="C34" s="10" t="inlineStr">
+        <is>
+          <t>Buffet</t>
+        </is>
+      </c>
+      <c r="D34" s="11" t="n"/>
+      <c r="E34" s="12" t="n"/>
+      <c r="F34" s="11" t="n"/>
+      <c r="G34" s="13" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>Reponer platos calientes cada 20-30 min (no dejar vacíos)</t>
+          <t>Montar estación de bollería y panes con tostadora</t>
         </is>
       </c>
       <c r="C35" s="10" t="inlineStr">
@@ -1299,11 +1413,11 @@
     </row>
     <row r="36">
       <c r="A36" s="8" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B36" s="9" t="inlineStr">
         <is>
-          <t>Reponer fruta, bollería y panes según consumo</t>
+          <t>Montar estación de cereales, leche, muesli y toppings</t>
         </is>
       </c>
       <c r="C36" s="10" t="inlineStr">
@@ -1318,16 +1432,16 @@
     </row>
     <row r="37">
       <c r="A37" s="8" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>Mantener limpieza continua del buffet: limpiar derrames inmediatamente</t>
-        </is>
-      </c>
-      <c r="C37" s="16" t="inlineStr">
-        <is>
-          <t>Limpieza</t>
+          <t>Verificar estación de bebidas: café, té, leche, zumos, agua</t>
+        </is>
+      </c>
+      <c r="C37" s="10" t="inlineStr">
+        <is>
+          <t>Buffet</t>
         </is>
       </c>
       <c r="D37" s="11" t="n"/>
@@ -1337,11 +1451,11 @@
     </row>
     <row r="38">
       <c r="A38" s="8" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="B38" s="9" t="inlineStr">
         <is>
-          <t>Reponer zumos, café y agua en la estación de bebidas</t>
+          <t>Colocar señalización con nombre de cada plato y alérgenos</t>
         </is>
       </c>
       <c r="C38" s="10" t="inlineStr">
@@ -1356,11 +1470,11 @@
     </row>
     <row r="39">
       <c r="A39" s="8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B39" s="9" t="inlineStr">
         <is>
-          <t>Retirar platos sucios de mesas de forma continua</t>
+          <t>Verificar mise en place de mesas: manteles, servilletas, cubiertos</t>
         </is>
       </c>
       <c r="C39" s="14" t="inlineStr">
@@ -1375,16 +1489,16 @@
     </row>
     <row r="40">
       <c r="A40" s="8" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>Controlar alérgenos: atender peticiones especiales (sin gluten, vegano)</t>
-        </is>
-      </c>
-      <c r="C40" s="10" t="inlineStr">
-        <is>
-          <t>Cocina</t>
+          <t>Colocar mermeladas, mantequilla, miel en cada mesa</t>
+        </is>
+      </c>
+      <c r="C40" s="14" t="inlineStr">
+        <is>
+          <t>Sala</t>
         </is>
       </c>
       <c r="D40" s="11" t="n"/>
@@ -1394,11 +1508,11 @@
     </row>
     <row r="41">
       <c r="A41" s="8" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B41" s="9" t="inlineStr">
         <is>
-          <t>Registrar conteo de comensales por tramos horarios</t>
+          <t>Verificar temperatura de sala (20-22 °C)</t>
         </is>
       </c>
       <c r="C41" s="15" t="inlineStr">
@@ -1411,77 +1525,77 @@
       <c r="F41" s="11" t="n"/>
       <c r="G41" s="13" t="n"/>
     </row>
-    <row r="42"/>
-    <row r="43">
-      <c r="A43" s="6" t="inlineStr">
-        <is>
-          <t>Cierre del buffet</t>
-        </is>
-      </c>
-    </row>
+    <row r="42">
+      <c r="A42" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="B42" s="9" t="inlineStr">
+        <is>
+          <t>Abrir buffet a la hora exacta según estándar del hotel</t>
+        </is>
+      </c>
+      <c r="C42" s="15" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D42" s="11" t="n"/>
+      <c r="E42" s="12" t="n"/>
+      <c r="F42" s="11" t="n"/>
+      <c r="G42" s="13" t="n"/>
+    </row>
+    <row r="43"/>
     <row r="44">
-      <c r="A44" s="7" t="inlineStr">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>Durante el servicio de desayuno</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="7" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B44" s="7" t="inlineStr">
+      <c r="B45" s="7" t="inlineStr">
         <is>
           <t>Tarea</t>
         </is>
       </c>
-      <c r="C44" s="7" t="inlineStr">
+      <c r="C45" s="7" t="inlineStr">
         <is>
           <t>Zona</t>
         </is>
       </c>
-      <c r="D44" s="7" t="inlineStr">
+      <c r="D45" s="7" t="inlineStr">
         <is>
           <t>Responsable</t>
         </is>
       </c>
-      <c r="E44" s="7" t="inlineStr">
+      <c r="E45" s="7" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F44" s="7" t="inlineStr">
+      <c r="F45" s="7" t="inlineStr">
         <is>
           <t>Hora</t>
         </is>
       </c>
-      <c r="G44" s="7" t="inlineStr">
+      <c r="G45" s="7" t="inlineStr">
         <is>
           <t>Notas</t>
         </is>
       </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="B45" s="9" t="inlineStr">
-        <is>
-          <t>Retirar señalización 10 min antes del cierre</t>
-        </is>
-      </c>
-      <c r="C45" s="10" t="inlineStr">
-        <is>
-          <t>Buffet</t>
-        </is>
-      </c>
-      <c r="D45" s="11" t="n"/>
-      <c r="E45" s="12" t="n"/>
-      <c r="F45" s="11" t="n"/>
-      <c r="G45" s="13" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B46" s="9" t="inlineStr">
         <is>
-          <t>Retirar gradualmente estaciones según política del hotel</t>
+          <t>Reponer platos calientes cada 20-30 min (no dejar vacíos)</t>
         </is>
       </c>
       <c r="C46" s="10" t="inlineStr">
@@ -1496,16 +1610,16 @@
     </row>
     <row r="47">
       <c r="A47" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B47" s="9" t="inlineStr">
         <is>
-          <t>Registrar sobrantes y mermas para ajustar producción futura</t>
+          <t>Reponer fruta, bollería y panes según consumo</t>
         </is>
       </c>
       <c r="C47" s="10" t="inlineStr">
         <is>
-          <t>Cocina</t>
+          <t>Buffet</t>
         </is>
       </c>
       <c r="D47" s="11" t="n"/>
@@ -1515,11 +1629,11 @@
     </row>
     <row r="48">
       <c r="A48" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B48" s="9" t="inlineStr">
         <is>
-          <t>Desmontar chafing dishes, limpiar y guardar</t>
+          <t>Mantener limpieza continua del buffet: limpiar derrames inmediatamente</t>
         </is>
       </c>
       <c r="C48" s="16" t="inlineStr">
@@ -1534,16 +1648,16 @@
     </row>
     <row r="49">
       <c r="A49" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B49" s="9" t="inlineStr">
         <is>
-          <t>Limpiar y desinfectar todas las superficies del buffet</t>
-        </is>
-      </c>
-      <c r="C49" s="16" t="inlineStr">
-        <is>
-          <t>Limpieza</t>
+          <t>Reponer zumos, café y agua en la estación de bebidas</t>
+        </is>
+      </c>
+      <c r="C49" s="10" t="inlineStr">
+        <is>
+          <t>Buffet</t>
         </is>
       </c>
       <c r="D49" s="11" t="n"/>
@@ -1553,16 +1667,16 @@
     </row>
     <row r="50">
       <c r="A50" s="8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B50" s="9" t="inlineStr">
         <is>
-          <t>Limpiar sala de desayunos: mesas, suelos, cristales</t>
-        </is>
-      </c>
-      <c r="C50" s="16" t="inlineStr">
-        <is>
-          <t>Limpieza</t>
+          <t>Retirar platos sucios de mesas de forma continua</t>
+        </is>
+      </c>
+      <c r="C50" s="14" t="inlineStr">
+        <is>
+          <t>Sala</t>
         </is>
       </c>
       <c r="D50" s="11" t="n"/>
@@ -1572,11 +1686,11 @@
     </row>
     <row r="51">
       <c r="A51" s="8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B51" s="9" t="inlineStr">
         <is>
-          <t>Preparar mise en place para el día siguiente (pedidos, preparaciones)</t>
+          <t>Controlar alérgenos: atender peticiones especiales (sin gluten, vegano)</t>
         </is>
       </c>
       <c r="C51" s="10" t="inlineStr">
@@ -1590,58 +1704,256 @@
       <c r="G51" s="13" t="n"/>
     </row>
     <row r="52">
-      <c r="B52" s="18" t="inlineStr">
+      <c r="A52" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B52" s="9" t="inlineStr">
+        <is>
+          <t>Registrar conteo de comensales por tramos horarios</t>
+        </is>
+      </c>
+      <c r="C52" s="15" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D52" s="11" t="n"/>
+      <c r="E52" s="12" t="n"/>
+      <c r="F52" s="11" t="n"/>
+      <c r="G52" s="13" t="n"/>
+    </row>
+    <row r="53"/>
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>Cierre del buffet</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="7" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C55" s="7" t="inlineStr">
+        <is>
+          <t>Zona</t>
+        </is>
+      </c>
+      <c r="D55" s="7" t="inlineStr">
+        <is>
+          <t>Responsable</t>
+        </is>
+      </c>
+      <c r="E55" s="7" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F55" s="7" t="inlineStr">
+        <is>
+          <t>Hora</t>
+        </is>
+      </c>
+      <c r="G55" s="7" t="inlineStr">
+        <is>
+          <t>Notas</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B56" s="9" t="inlineStr">
+        <is>
+          <t>Retirar señalización 10 min antes del cierre</t>
+        </is>
+      </c>
+      <c r="C56" s="10" t="inlineStr">
+        <is>
+          <t>Buffet</t>
+        </is>
+      </c>
+      <c r="D56" s="11" t="n"/>
+      <c r="E56" s="12" t="n"/>
+      <c r="F56" s="11" t="n"/>
+      <c r="G56" s="13" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B57" s="9" t="inlineStr">
+        <is>
+          <t>Retirar gradualmente estaciones según política del hotel</t>
+        </is>
+      </c>
+      <c r="C57" s="10" t="inlineStr">
+        <is>
+          <t>Buffet</t>
+        </is>
+      </c>
+      <c r="D57" s="11" t="n"/>
+      <c r="E57" s="12" t="n"/>
+      <c r="F57" s="11" t="n"/>
+      <c r="G57" s="13" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B58" s="9" t="inlineStr">
+        <is>
+          <t>Registrar sobrantes y mermas para ajustar producción futura</t>
+        </is>
+      </c>
+      <c r="C58" s="10" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D58" s="11" t="n"/>
+      <c r="E58" s="12" t="n"/>
+      <c r="F58" s="11" t="n"/>
+      <c r="G58" s="13" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B59" s="9" t="inlineStr">
+        <is>
+          <t>Desmontar chafing dishes, limpiar y guardar</t>
+        </is>
+      </c>
+      <c r="C59" s="16" t="inlineStr">
+        <is>
+          <t>Limpieza</t>
+        </is>
+      </c>
+      <c r="D59" s="11" t="n"/>
+      <c r="E59" s="12" t="n"/>
+      <c r="F59" s="11" t="n"/>
+      <c r="G59" s="13" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B60" s="9" t="inlineStr">
+        <is>
+          <t>Limpiar y desinfectar todas las superficies del buffet</t>
+        </is>
+      </c>
+      <c r="C60" s="16" t="inlineStr">
+        <is>
+          <t>Limpieza</t>
+        </is>
+      </c>
+      <c r="D60" s="11" t="n"/>
+      <c r="E60" s="12" t="n"/>
+      <c r="F60" s="11" t="n"/>
+      <c r="G60" s="13" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B61" s="9" t="inlineStr">
+        <is>
+          <t>Limpiar sala de desayunos: mesas, suelos, cristales</t>
+        </is>
+      </c>
+      <c r="C61" s="16" t="inlineStr">
+        <is>
+          <t>Limpieza</t>
+        </is>
+      </c>
+      <c r="D61" s="11" t="n"/>
+      <c r="E61" s="12" t="n"/>
+      <c r="F61" s="11" t="n"/>
+      <c r="G61" s="13" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B62" s="9" t="inlineStr">
+        <is>
+          <t>Preparar mise en place para el día siguiente (pedidos, preparaciones)</t>
+        </is>
+      </c>
+      <c r="C62" s="10" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D62" s="11" t="n"/>
+      <c r="E62" s="12" t="n"/>
+      <c r="F62" s="11" t="n"/>
+      <c r="G62" s="13" t="n"/>
+    </row>
+    <row r="63">
+      <c r="B63" s="18" t="inlineStr">
         <is>
           <t>Tareas completadas:</t>
         </is>
       </c>
-      <c r="C52">
-        <f>COUNTIF(E6:E51,"✓")</f>
-        <v>3.0</v>
-      </c>
-      <c r="D52" t="inlineStr">
+      <c r="C63">
+        <f>COUNTIFS(B6:B62,"?*",E6:E62,"✓")-COUNTIFS(B6:B62,"Tarea",E6:E62,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="D63" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="E52">
-        <f>COUNTIF(B6:B51,"?*")</f>
-        <v>40.0</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="17" t="inlineStr">
+      <c r="E63">
+        <f>COUNTIF(B6:B62,"?*")-COUNTIF(B6:B62,"Tarea")-COUNTIF(E6:E62,"N/A")</f>
+        <v>46.0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="17" t="inlineStr">
         <is>
           <t>Firma responsable: _________________  Fecha: ___/___/______</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="17" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="17" t="inlineStr">
         <is>
           <t>© 2026 AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
+    <mergeCell ref="A44:G44"/>
+    <mergeCell ref="A1:G1"/>
     <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A33:G33"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A53:G53"/>
+    <mergeCell ref="A28:G28"/>
+    <mergeCell ref="A65:G65"/>
+    <mergeCell ref="A64:G64"/>
+    <mergeCell ref="A14:G14"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A18:G18"/>
-    <mergeCell ref="A43:G43"/>
     <mergeCell ref="A54:G54"/>
   </mergeCells>
-  <conditionalFormatting sqref="A6:G51">
+  <conditionalFormatting sqref="A6:G62">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$E6="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E12 E13 E14 E15 E16 E20 E21 E22 E23 E24 E25 E26 E27 E28 E29 E30 E31 E35 E36 E37 E38 E39 E40 E41 E45 E46 E47 E48 E49 E50 E51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
-      <formula1>"✓,✗,—"</formula1>
+    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E12 E13 E16 E17 E18 E19 E20 E21 E22 E23 E24 E25 E26 E30 E31 E32 E33 E34 E35 E36 E37 E38 E39 E40 E41 E42 E46 E47 E48 E49 E50 E51 E52 E56 E57 E58 E59 E60 E61 E62" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." prompt="Marca ✓ si completada" type="list" errorStyle="stop">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
@@ -1664,7 +1976,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1760,7 +2072,7 @@
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>Separar producto reutilizable (sin contaminar) de merma</t>
+          <t>Separar producto reutilizable de merma: lo que ha estado EXPUESTO en la línea del buffet (al alcance del cliente o fuera de temperatura) se retira; sólo vuelve a cámara lo que no ha salido del office y ha mantenido la cadena de frío o de calor</t>
         </is>
       </c>
       <c r="C7" s="10" t="inlineStr">
@@ -1779,7 +2091,7 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>Etiquetar producto reutilizable con fecha y temperatura</t>
+          <t>Etiquetar el producto reutilizable con el nombre, la fecha y la hora, y guardarlo tapado en refrigeración 0-4 °C: la vida útil por familia está en la tabla del pie de esta hoja</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
@@ -1957,7 +2269,7 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>Limpiar y desinfectar estación de zumos y café</t>
+          <t>Limpiar y desinfectar la estación de zumos y café: ejecutar el ciclo de limpieza de la cafetera (pastilla detergente o backflush del grupo, según el modelo), lavar el circuito y la jarra de leche, y desmontar y fregar la exprimidora</t>
         </is>
       </c>
       <c r="C18" s="16" t="inlineStr">
@@ -2174,8 +2486,8 @@
         </is>
       </c>
       <c r="C30">
-        <f>COUNTIF(E6:E29,"✓")</f>
-        <v>2.0</v>
+        <f>COUNTIFS(B6:B29,"?*",E6:E29,"✓")-COUNTIFS(B6:B29,"Tarea",E6:E29,"✓")</f>
+        <v>0.0</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2183,8 +2495,8 @@
         </is>
       </c>
       <c r="E30">
-        <f>COUNTIF(B6:B29,"?*")</f>
-        <v>20.0</v>
+        <f>COUNTIF(B6:B29,"?*")-COUNTIF(B6:B29,"Tarea")-COUNTIF(E6:E29,"N/A")</f>
+        <v>18.0</v>
       </c>
     </row>
     <row r="31">
@@ -2195,19 +2507,250 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="17" t="inlineStr">
+      <c r="A32" s="17" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>VIDA ÚTIL ORIENTATIVA EN CONGELACIÓN A −18 °C — ajústala a tu producto y a tu proveedor</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="n"/>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>Familia</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>Vida útil</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>Notas</t>
+        </is>
+      </c>
+      <c r="E34" s="19" t="n"/>
+      <c r="F34" s="19" t="n"/>
+      <c r="G34" s="20" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="8" t="n"/>
+      <c r="B35" s="21" t="inlineStr">
+        <is>
+          <t>Carnes rojas y aves crudas, en pieza</t>
+        </is>
+      </c>
+      <c r="C35" s="22" t="inlineStr">
+        <is>
+          <t>6-12 meses</t>
+        </is>
+      </c>
+      <c r="D35" s="23" t="inlineStr">
+        <is>
+          <t>Porciona ANTES de congelar: descongelar y volver a congelar no se hace</t>
+        </is>
+      </c>
+      <c r="E35" s="19" t="n"/>
+      <c r="F35" s="19" t="n"/>
+      <c r="G35" s="20" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="8" t="n"/>
+      <c r="B36" s="21" t="inlineStr">
+        <is>
+          <t>Carne picada y preparados de carne</t>
+        </is>
+      </c>
+      <c r="C36" s="22" t="inlineStr">
+        <is>
+          <t>3 meses</t>
+        </is>
+      </c>
+      <c r="D36" s="23" t="inlineStr">
+        <is>
+          <t>Más superficie expuesta: se enrancia y se oxida mucho antes que la pieza entera</t>
+        </is>
+      </c>
+      <c r="E36" s="19" t="n"/>
+      <c r="F36" s="19" t="n"/>
+      <c r="G36" s="20" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="8" t="n"/>
+      <c r="B37" s="21" t="inlineStr">
+        <is>
+          <t>Pescado blanco y marisco crudo</t>
+        </is>
+      </c>
+      <c r="C37" s="22" t="inlineStr">
+        <is>
+          <t>3-6 meses</t>
+        </is>
+      </c>
+      <c r="D37" s="23" t="inlineStr">
+        <is>
+          <t>El tratamiento antianisakis (≥ 24 h a −20 °C) no sustituye a esta vida útil: se cuentan por separado</t>
+        </is>
+      </c>
+      <c r="E37" s="19" t="n"/>
+      <c r="F37" s="19" t="n"/>
+      <c r="G37" s="20" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="8" t="n"/>
+      <c r="B38" s="21" t="inlineStr">
+        <is>
+          <t>Pescado azul (salmón, atún, boquerón)</t>
+        </is>
+      </c>
+      <c r="C38" s="22" t="inlineStr">
+        <is>
+          <t>2-3 meses</t>
+        </is>
+      </c>
+      <c r="D38" s="23" t="inlineStr">
+        <is>
+          <t>La grasa se enrancia aunque esté congelado: es el que antes se estropea</t>
+        </is>
+      </c>
+      <c r="E38" s="19" t="n"/>
+      <c r="F38" s="19" t="n"/>
+      <c r="G38" s="20" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="8" t="n"/>
+      <c r="B39" s="21" t="inlineStr">
+        <is>
+          <t>Fondos, salsas y cremas de elaboración propia</t>
+        </is>
+      </c>
+      <c r="C39" s="22" t="inlineStr">
+        <is>
+          <t>3 meses</t>
+        </is>
+      </c>
+      <c r="D39" s="23" t="inlineStr">
+        <is>
+          <t>Etiqueta con la fecha de producción Y la de congelación: la vida útil se cuenta desde la de congelación</t>
+        </is>
+      </c>
+      <c r="E39" s="19" t="n"/>
+      <c r="F39" s="19" t="n"/>
+      <c r="G39" s="20" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="8" t="n"/>
+      <c r="B40" s="21" t="inlineStr">
+        <is>
+          <t>Masas, bases de tarta y hojaldre crudos</t>
+        </is>
+      </c>
+      <c r="C40" s="22" t="inlineStr">
+        <is>
+          <t>1-2 meses</t>
+        </is>
+      </c>
+      <c r="D40" s="23" t="inlineStr">
+        <is>
+          <t>La levadura pierde fuerza: después sube mal aunque siga siendo seguro</t>
+        </is>
+      </c>
+      <c r="E40" s="19" t="n"/>
+      <c r="F40" s="19" t="n"/>
+      <c r="G40" s="20" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="8" t="n"/>
+      <c r="B41" s="21" t="inlineStr">
+        <is>
+          <t>Bollería y pan ya horneados</t>
+        </is>
+      </c>
+      <c r="C41" s="22" t="inlineStr">
+        <is>
+          <t>1-3 meses</t>
+        </is>
+      </c>
+      <c r="D41" s="23" t="inlineStr">
+        <is>
+          <t>Pierde textura antes que seguridad; regenera en horno, nunca en microondas</t>
+        </is>
+      </c>
+      <c r="E41" s="19" t="n"/>
+      <c r="F41" s="19" t="n"/>
+      <c r="G41" s="20" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="8" t="n"/>
+      <c r="B42" s="21" t="inlineStr">
+        <is>
+          <t>Verdura blanqueada, purés y guarniciones</t>
+        </is>
+      </c>
+      <c r="C42" s="22" t="inlineStr">
+        <is>
+          <t>8-12 meses</t>
+        </is>
+      </c>
+      <c r="D42" s="23" t="inlineStr">
+        <is>
+          <t>Blanquea antes de congelar: sin blanquear pierde color y textura en pocas semanas</t>
+        </is>
+      </c>
+      <c r="E42" s="19" t="n"/>
+      <c r="F42" s="19" t="n"/>
+      <c r="G42" s="20" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="8" t="n"/>
+      <c r="B43" s="21" t="inlineStr">
+        <is>
+          <t>Producto que ya ha salido a la línea del buffet</t>
+        </is>
+      </c>
+      <c r="C43" s="22" t="inlineStr">
+        <is>
+          <t>No congelar</t>
+        </is>
+      </c>
+      <c r="D43" s="23" t="inlineStr">
+        <is>
+          <t>Lo expuesto en sala o servido por el cliente no vuelve al congelador: se retira</t>
+        </is>
+      </c>
+      <c r="E43" s="19" t="n"/>
+      <c r="F43" s="19" t="n"/>
+      <c r="G43" s="20" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="17" t="inlineStr">
         <is>
           <t>© 2026 AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="18">
+    <mergeCell ref="D36:G36"/>
     <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A44:G44"/>
+    <mergeCell ref="A31:G31"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A31:G31"/>
-    <mergeCell ref="A32:G32"/>
+    <mergeCell ref="A33:G33"/>
+    <mergeCell ref="D37:G37"/>
+    <mergeCell ref="D38:G38"/>
+    <mergeCell ref="D42:G42"/>
+    <mergeCell ref="D43:G43"/>
     <mergeCell ref="A2:G2"/>
+    <mergeCell ref="D39:G39"/>
+    <mergeCell ref="D41:G41"/>
+    <mergeCell ref="D34:G34"/>
+    <mergeCell ref="D40:G40"/>
+    <mergeCell ref="D35:G35"/>
     <mergeCell ref="A13:G13"/>
     <mergeCell ref="A22:G22"/>
   </mergeCells>
@@ -2217,8 +2760,8 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E15 E16 E17 E18 E19 E20 E24 E25 E26 E27 E28 E29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
-      <formula1>"✓,✗,—"</formula1>
+    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E15 E16 E17 E18 E19 E20 E24 E25 E26 E27 E28 E29" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." prompt="Marca ✓ si completada" type="list" errorStyle="stop">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>

--- a/astro-site/public/dl/kit-tareas-hotel/01-fb-buffet-desayuno.xlsx
+++ b/astro-site/public/dl/kit-tareas-hotel/01-fb-buffet-desayuno.xlsx
@@ -1937,10 +1937,10 @@
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="A44:G44"/>
+    <mergeCell ref="A28:G28"/>
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A65:G65"/>
     <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A28:G28"/>
-    <mergeCell ref="A65:G65"/>
     <mergeCell ref="A64:G64"/>
     <mergeCell ref="A14:G14"/>
     <mergeCell ref="A2:G2"/>
@@ -2741,16 +2741,16 @@
     <mergeCell ref="A31:G31"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A33:G33"/>
-    <mergeCell ref="D37:G37"/>
     <mergeCell ref="D38:G38"/>
     <mergeCell ref="D42:G42"/>
-    <mergeCell ref="D43:G43"/>
+    <mergeCell ref="D35:G35"/>
+    <mergeCell ref="D37:G37"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="D39:G39"/>
     <mergeCell ref="D41:G41"/>
     <mergeCell ref="D34:G34"/>
     <mergeCell ref="D40:G40"/>
-    <mergeCell ref="D35:G35"/>
+    <mergeCell ref="D43:G43"/>
     <mergeCell ref="A13:G13"/>
     <mergeCell ref="A22:G22"/>
   </mergeCells>
